--- a/assets/Catalogo_Perfumes.xlsx
+++ b/assets/Catalogo_Perfumes.xlsx
@@ -546,7 +546,7 @@
         <v>900</v>
       </c>
       <c r="G2" t="n">
-        <v>840</v>
+        <v>1170</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         <v>850</v>
       </c>
       <c r="G3" t="n">
-        <v>800</v>
+        <v>1110</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -634,7 +634,7 @@
         <v>1050</v>
       </c>
       <c r="G4" t="n">
-        <v>990</v>
+        <v>1370</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         <v>1190</v>
       </c>
       <c r="G5" t="n">
-        <v>1300</v>
+        <v>1550</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>1100</v>
       </c>
       <c r="G13" t="n">
-        <v>1086</v>
+        <v>1430</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         <v>1190</v>
       </c>
       <c r="G17" t="n">
-        <v>1508</v>
+        <v>1550</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>1190</v>
       </c>
       <c r="G18" t="n">
-        <v>1508</v>
+        <v>1550</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>1090</v>
       </c>
       <c r="G28" t="n">
-        <v>1200</v>
+        <v>1420</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>1130</v>
       </c>
       <c r="G31" t="n">
-        <v>1430</v>
+        <v>1470</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
         <v>2850</v>
       </c>
       <c r="G36" t="n">
-        <v>3300</v>
+        <v>3710</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>2490</v>
       </c>
       <c r="G40" t="n">
-        <v>2990</v>
+        <v>3240</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>2790</v>
       </c>
       <c r="G41" t="n">
-        <v>3090</v>
+        <v>3630</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>1590</v>
       </c>
       <c r="G43" t="n">
-        <v>1990</v>
+        <v>2070</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>1890</v>
       </c>
       <c r="G48" t="n">
-        <v>2450</v>
+        <v>2460</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>1850</v>
       </c>
       <c r="G52" t="n">
-        <v>2300</v>
+        <v>2410</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>2090</v>
       </c>
       <c r="G53" t="n">
-        <v>2550</v>
+        <v>2720</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>2190</v>
       </c>
       <c r="G57" t="n">
-        <v>2800</v>
+        <v>2850</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>1790</v>
       </c>
       <c r="G58" t="n">
-        <v>2300</v>
+        <v>2330</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         <v>2290</v>
       </c>
       <c r="G60" t="n">
-        <v>2915</v>
+        <v>2980</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>2390</v>
       </c>
       <c r="G61" t="n">
-        <v>2990</v>
+        <v>3110</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>2690</v>
       </c>
       <c r="G62" t="n">
-        <v>3490</v>
+        <v>3500</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>2990</v>
       </c>
       <c r="G64" t="n">
-        <v>3490</v>
+        <v>3890</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>2690</v>
       </c>
       <c r="G65" t="n">
-        <v>2990</v>
+        <v>3500</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>2690</v>
       </c>
       <c r="G92" t="n">
-        <v>3420</v>
+        <v>3500</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>890</v>
       </c>
       <c r="G112" t="n">
-        <v>940</v>
+        <v>1160</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>1190</v>
       </c>
       <c r="G129" t="n">
-        <v>1390</v>
+        <v>1550</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>1790</v>
       </c>
       <c r="G132" t="n">
-        <v>2100</v>
+        <v>2330</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>2390</v>
       </c>
       <c r="G135" t="n">
-        <v>2440</v>
+        <v>3110</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>2190</v>
       </c>
       <c r="G136" t="n">
-        <v>2740</v>
+        <v>2850</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>2290</v>
       </c>
       <c r="G141" t="n">
-        <v>2820</v>
+        <v>2980</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>2090</v>
       </c>
       <c r="G142" t="n">
-        <v>2360</v>
+        <v>2720</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>7000</v>
       </c>
       <c r="G145" t="n">
-        <v>8200</v>
+        <v>9100</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>990</v>
       </c>
       <c r="G148" t="n">
-        <v>1000</v>
+        <v>1290</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -7416,7 +7416,7 @@
         <v>3390</v>
       </c>
       <c r="G160" t="n">
-        <v>4090</v>
+        <v>4410</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>3090</v>
       </c>
       <c r="G162" t="n">
-        <v>3750</v>
+        <v>4020</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>5500</v>
       </c>
       <c r="G178" t="n">
-        <v>6600</v>
+        <v>7150</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>5500</v>
       </c>
       <c r="G179" t="n">
-        <v>6600</v>
+        <v>7150</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         <v>1590</v>
       </c>
       <c r="G3" t="n">
-        <v>1900</v>
+        <v>2070</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>1690</v>
       </c>
       <c r="G5" t="n">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -9159,7 +9159,7 @@
         <v>1490</v>
       </c>
       <c r="G15" t="n">
-        <v>1900</v>
+        <v>1940</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>3090</v>
       </c>
       <c r="G17" t="n">
-        <v>3800</v>
+        <v>4020</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>1590</v>
       </c>
       <c r="G33" t="n">
-        <v>1398</v>
+        <v>2070</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>1490</v>
       </c>
       <c r="G44" t="n">
-        <v>1700</v>
+        <v>1940</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>1390</v>
       </c>
       <c r="G75" t="n">
-        <v>1500</v>
+        <v>1810</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
